--- a/docs/command.xlsx
+++ b/docs/command.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trade\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{798544FA-7D11-4C39-B534-DA837AFDF268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BD39B6-D14E-4AD4-A020-609325472EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF08F339-BCB1-417D-8A7F-74E9DE117E73}"/>
+    <workbookView xWindow="1770" yWindow="1770" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{EF08F339-BCB1-417D-8A7F-74E9DE117E73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Task</t>
   </si>
@@ -61,6 +63,114 @@
   </si>
   <si>
     <t>git pull &amp;&amp; docker-compose up -d --build</t>
+  </si>
+  <si>
+    <t>Epic Overview (Development Order)</t>
+  </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Key Deliverables</t>
+  </si>
+  <si>
+    <t>E0: Foundation</t>
+  </si>
+  <si>
+    <t>Project structure, DB setup, Redis, Docker, Next.js scaffold, dark theme</t>
+  </si>
+  <si>
+    <t>E1: Auth</t>
+  </si>
+  <si>
+    <t>JWT login, API key CRUD, RBAC, rate limiting, login page</t>
+  </si>
+  <si>
+    <t>E2: Trading Engine</t>
+  </si>
+  <si>
+    <t>Platform adapter interface, MT5 refactor, trade service, dashboard</t>
+  </si>
+  <si>
+    <t>E3: AI Providers</t>
+  </si>
+  <si>
+    <t>AI adapter interface, OpenRouter + NVIDIA NIM, switch from UI</t>
+  </si>
+  <si>
+    <t>E4: Real-time</t>
+  </si>
+  <si>
+    <t>WebSocket hub, Redis pub/sub, live prices/logs/trades</t>
+  </si>
+  <si>
+    <t>E5: Bot Control</t>
+  </si>
+  <si>
+    <t>Start/stop/restart, settings, Celery trade loop</t>
+  </si>
+  <si>
+    <t>E6: Analytics</t>
+  </si>
+  <si>
+    <t>Equity curves, P&amp;L charts, performance metrics</t>
+  </si>
+  <si>
+    <t>E7: Multi-Platform</t>
+  </si>
+  <si>
+    <t>Bitkub adapter, Binance adapter, 24h crypto support</t>
+  </si>
+  <si>
+    <t>E8: MCP</t>
+  </si>
+  <si>
+    <t>MCP client, webhook system, n8n integration</t>
+  </si>
+  <si>
+    <t>E9: Hardening</t>
+  </si>
+  <si>
+    <t>Tests (≥80%), security audit, performance optimization</t>
+  </si>
+  <si>
+    <t>./go dev             # start everything</t>
+  </si>
+  <si>
+    <t>./go backend         # backend + db + redis</t>
+  </si>
+  <si>
+    <t>./go logs backend    # tail specific service</t>
+  </si>
+  <si>
+    <t>./go shell back      # shell into backend</t>
+  </si>
+  <si>
+    <t>./go test            # run tests</t>
+  </si>
+  <si>
+    <t>./go down            # stop all</t>
+  </si>
+  <si>
+    <t>.\x.ps1 dev          # same commands</t>
+  </si>
+  <si>
+    <t>.\x.ps1 backend</t>
+  </si>
+  <si>
+    <t>.\x.ps1 logs-back</t>
+  </si>
+  <si>
+    <t>.\x.ps1 shell-back</t>
+  </si>
+  <si>
+    <t>.\x.ps1 test</t>
+  </si>
+  <si>
+    <t>.\x.ps1 down</t>
   </si>
 </sst>
 </file>
@@ -137,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -147,6 +257,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -469,7 +583,7 @@
     <col min="2" max="2" width="39.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29.25" thickBot="1">
+    <row r="1" spans="1:2" ht="15.75" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,6 +629,225 @@
       </c>
       <c r="B6" s="3" t="s">
         <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA643CD0-C3E5-4F57-ABA5-BF44E3BAC030}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4">
+        <v>46054</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4">
+        <v>46083</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4">
+        <v>46115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4">
+        <v>46146</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4">
+        <v>46241</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4">
+        <v>46303</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4">
+        <v>46336</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4">
+        <v>46367</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD4731E0-A831-4A34-BC76-348F39937C49}">
+  <dimension ref="A1:A14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
